--- a/d/2026-09-02_会员有效性分析.xlsx
+++ b/d/2026-09-02_会员有效性分析.xlsx
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C3" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>95.02</v>
+        <v>95.05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.98</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="4">
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -732,25 +732,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
         <v>9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>22.22</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>8.33</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="7">
@@ -786,25 +786,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="8">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2433,19 +2433,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>APR北京北苑龙湖</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2460,19 +2460,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2487,19 +2487,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>APR北京北苑龙湖</t>
+          <t>DJI上海徐汇万科广场授权体验店</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -5530,12 +5530,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5556,7 +5556,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6942103183102</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183102</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -8907,12 +8907,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -9842,12 +9842,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -10117,12 +10117,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -10612,12 +10612,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -10667,12 +10667,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -10722,12 +10722,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -10832,12 +10832,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -11162,12 +11162,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -11217,12 +11217,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -11327,12 +11327,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -11602,12 +11602,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -11712,12 +11712,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -11767,12 +11767,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -11877,12 +11877,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -12152,12 +12152,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -12207,12 +12207,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -12317,12 +12317,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -12372,12 +12372,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -12427,12 +12427,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -12592,12 +12592,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -12812,12 +12812,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -13087,12 +13087,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -13142,12 +13142,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -13472,12 +13472,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -13802,12 +13802,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -13912,12 +13912,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -14022,12 +14022,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -14077,12 +14077,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -14187,12 +14187,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -14682,12 +14682,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -14792,12 +14792,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -15232,12 +15232,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -15287,12 +15287,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -15452,12 +15452,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -15617,12 +15617,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -15727,12 +15727,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -15782,12 +15782,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -15892,12 +15892,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -16002,12 +16002,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -16057,12 +16057,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K153" t="n">
@@ -16112,12 +16112,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K154" t="n">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -16277,12 +16277,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K159" t="n">
@@ -16442,12 +16442,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K160" t="n">
@@ -16497,12 +16497,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K161" t="n">
@@ -17157,12 +17157,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183126</t>
         </is>
       </c>
       <c r="K173" t="n">
@@ -17212,12 +17212,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>6942103183126</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K174" t="n">
@@ -17267,12 +17267,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -17322,12 +17322,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K176" t="n">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -17432,12 +17432,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K178" t="n">
@@ -17487,12 +17487,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K180" t="n">
@@ -17597,12 +17597,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K181" t="n">
@@ -17707,12 +17707,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -17762,12 +17762,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K184" t="n">
@@ -17872,12 +17872,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K186" t="n">
@@ -17927,12 +17927,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -18037,12 +18037,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K189" t="n">
@@ -18092,12 +18092,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K190" t="n">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K191" t="n">
@@ -18202,12 +18202,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -18532,12 +18532,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K198" t="n">
@@ -18587,12 +18587,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -18642,12 +18642,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K200" t="n">
@@ -18697,12 +18697,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K201" t="n">
@@ -18752,12 +18752,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -18807,12 +18807,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -18917,12 +18917,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K205" t="n">
@@ -18972,12 +18972,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K206" t="n">
@@ -19192,12 +19192,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K210" t="n">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K211" t="n">
@@ -19357,12 +19357,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K213" t="n">
@@ -19412,12 +19412,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K214" t="n">
@@ -19467,12 +19467,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K215" t="n">
@@ -19577,12 +19577,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -19632,12 +19632,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K218" t="n">
@@ -19742,12 +19742,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K220" t="n">
@@ -19797,12 +19797,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K221" t="n">
@@ -20591,12 +20591,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>195****64870</t>
+          <t>195****64757</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -20662,12 +20662,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>195****64757</t>
+          <t>195****64870</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -20870,17 +20870,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6922329935952</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -20946,12 +20946,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
+          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6922329935587</t>
+          <t>6922329935952</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -21017,12 +21017,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>6922329935587</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -21083,17 +21083,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -21159,12 +21159,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6955482539514</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -21230,12 +21230,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482539514</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -21296,17 +21296,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -21367,17 +21367,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6937045847984</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -21438,17 +21438,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6955482533109</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -21509,17 +21509,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6955482533109</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -21585,12 +21585,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6927123805548</t>
+          <t>6937045847984</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -21651,17 +21651,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6927123805548</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -21935,17 +21935,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -22006,17 +22006,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -22792,12 +22792,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>6927123810382</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -22858,17 +22858,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -22929,17 +22929,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6927123810382</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -23071,17 +23071,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FPV</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>DJI Neo 2（仅飞行器）</t>
+          <t>DJI 无纺布购物袋（中号）</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>6937224131767</t>
+          <t>6937224129511</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -23142,17 +23142,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>FPV</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（中号）</t>
+          <t>DJI Neo 2（仅飞行器）</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>6937224129511</t>
+          <t>6937224131767</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -26183,17 +26183,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -26254,17 +26254,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -26330,12 +26330,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -26396,17 +26396,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -26472,12 +26472,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -26538,17 +26538,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -26609,17 +26609,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>线缆</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>60W USB-C 充电线 (1 米) - 无塑料包装-MW493FE/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>195****71875</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -26680,17 +26680,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>线缆</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>60W USB-C 充电线 (1 米) - 无塑料包装-MW493FE/A</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****71875</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -27106,17 +27106,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>6955482530214</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -27182,12 +27182,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4895241136474</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -27253,12 +27253,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>4895241136474</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -27324,12 +27324,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>6955482530214</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -27390,17 +27390,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -27461,17 +27461,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -27750,12 +27750,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -27816,17 +27816,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -27892,12 +27892,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -27958,17 +27958,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -28029,17 +28029,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -28100,17 +28100,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -28176,12 +28176,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -28247,12 +28247,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -28313,17 +28313,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -28384,17 +28384,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -28455,17 +28455,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -28597,17 +28597,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -28673,12 +28673,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -28739,17 +28739,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 薄暮灰</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>6938741702959</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -28810,17 +28810,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 薄暮灰</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>6938741702959</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -28886,12 +28886,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -28952,17 +28952,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -29165,17 +29165,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
+          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>XMPZ202612189</t>
+          <t>195****28869</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -29236,17 +29236,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
+          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>195****28869</t>
+          <t>XMPZ202612189</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -29378,17 +29378,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 512GB 星宇橙色 - MG074CH/A</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41158</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -29449,17 +29449,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 512GB 星宇橙色 - MG074CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>195****41158</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -29667,12 +29667,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/粉色-MD4E4CH/A</t>
+          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>195****86836</t>
+          <t>195****86379</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -29735,12 +29735,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
+          <t>11 英寸 iPad GPS 128GB/粉色-MD4E4CH/A</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>195****86379</t>
+          <t>195****86836</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -29798,20 +29798,23 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>iPad基础版</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
+          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>195****86379</t>
+          <t>6923517323407</t>
         </is>
       </c>
       <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
         <v>1</v>
       </c>
       <c r="N135" t="n">
@@ -29866,23 +29869,20 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPad基础版</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
+          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>6923517323407</t>
+          <t>195****86379</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
-      </c>
-      <c r="M136" t="n">
         <v>1</v>
       </c>
       <c r="N136" t="n">
@@ -30013,12 +30013,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>6942297127241</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -30155,12 +30155,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6942297127241</t>
         </is>
       </c>
       <c r="L140" t="n">
